--- a/human_resources_forms/025_leadership_development_interview_form--human_resources_forms.xlsx
+++ b/human_resources_forms/025_leadership_development_interview_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>job_status</t>
+          <t>job_status_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>job status</t>
+          <t>Job Status 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>job title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>job_description_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>job description</t>
+          <t>Job Description 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'non-manager'}</t>
+          <t>non-manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'non-manager'}</t>
+          <t>non-manager</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'executive'}</t>
+          <t>executive</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'executive'}</t>
+          <t>executive</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'high school'}</t>
+          <t>high school</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'master'}</t>
+          <t>master</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'phd'}</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'phd'}</t>
+          <t>phd</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'problem solving'}</t>
+          <t>problem solving</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'high', 'label': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'frequent'}</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'frequent'}</t>
+          <t>frequent</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'occasional'}</t>
+          <t>occasional</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'occasional'}</t>
+          <t>occasional</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rare'}</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'rare'}</t>
+          <t>rare</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'full time'}</t>
+          <t>full time</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'part time'}</t>
+          <t>part time</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'small'}</t>
+          <t>small</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'large'}</t>
+          <t>large</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'local'}</t>
+          <t>local</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'active'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -1573,46 +1573,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'active'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'working'}</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'working'}</t>
+          <t>working</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_working'}</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'not working'}</t>
+          <t>not working</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'junior'}</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'junior'}</t>
+          <t>junior</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'part time'}</t>
+          <t>part time</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'full time'}</t>
+          <t>full time</t>
         </is>
       </c>
     </row>
